--- a/artfynd/Ornös nordspets artfynd.xlsx
+++ b/artfynd/Ornös nordspets artfynd.xlsx
@@ -23005,6 +23005,7 @@
       <c r="AE191" t="b">
         <v>0</v>
       </c>
+      <c r="AF191" t="inlineStr"/>
       <c r="AG191" t="b">
         <v>0</v>
       </c>
@@ -23016,7 +23017,7 @@
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Emilia Blixt, Elis Bergman , Sanna Blixt</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>

--- a/artfynd/Ornös nordspets artfynd.xlsx
+++ b/artfynd/Ornös nordspets artfynd.xlsx
@@ -22908,7 +22908,7 @@
         <v>136730156</v>
       </c>
       <c r="B191" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>

--- a/artfynd/Ornös nordspets artfynd.xlsx
+++ b/artfynd/Ornös nordspets artfynd.xlsx
@@ -22908,7 +22908,7 @@
         <v>136730156</v>
       </c>
       <c r="B191" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>

--- a/artfynd/Ornös nordspets artfynd.xlsx
+++ b/artfynd/Ornös nordspets artfynd.xlsx
@@ -22908,7 +22908,7 @@
         <v>136730156</v>
       </c>
       <c r="B191" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>

--- a/artfynd/Ornös nordspets artfynd.xlsx
+++ b/artfynd/Ornös nordspets artfynd.xlsx
@@ -22908,7 +22908,7 @@
         <v>136730156</v>
       </c>
       <c r="B191" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>

--- a/artfynd/Ornös nordspets artfynd.xlsx
+++ b/artfynd/Ornös nordspets artfynd.xlsx
@@ -22908,7 +22908,7 @@
         <v>136730156</v>
       </c>
       <c r="B191" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>

--- a/artfynd/Ornös nordspets artfynd.xlsx
+++ b/artfynd/Ornös nordspets artfynd.xlsx
@@ -22908,7 +22908,7 @@
         <v>136730156</v>
       </c>
       <c r="B191" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>

--- a/artfynd/Ornös nordspets artfynd.xlsx
+++ b/artfynd/Ornös nordspets artfynd.xlsx
@@ -22908,7 +22908,7 @@
         <v>136730156</v>
       </c>
       <c r="B191" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>

--- a/artfynd/Ornös nordspets artfynd.xlsx
+++ b/artfynd/Ornös nordspets artfynd.xlsx
@@ -22908,7 +22908,7 @@
         <v>136730156</v>
       </c>
       <c r="B191" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>

--- a/artfynd/Ornös nordspets artfynd.xlsx
+++ b/artfynd/Ornös nordspets artfynd.xlsx
@@ -22908,7 +22908,7 @@
         <v>136730156</v>
       </c>
       <c r="B191" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>

--- a/artfynd/Ornös nordspets artfynd.xlsx
+++ b/artfynd/Ornös nordspets artfynd.xlsx
@@ -22908,7 +22908,7 @@
         <v>136730156</v>
       </c>
       <c r="B191" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>

--- a/artfynd/Ornös nordspets artfynd.xlsx
+++ b/artfynd/Ornös nordspets artfynd.xlsx
@@ -22908,7 +22908,7 @@
         <v>136730156</v>
       </c>
       <c r="B191" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>

--- a/artfynd/Ornös nordspets artfynd.xlsx
+++ b/artfynd/Ornös nordspets artfynd.xlsx
@@ -22908,7 +22908,7 @@
         <v>136730156</v>
       </c>
       <c r="B191" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>

--- a/artfynd/Ornös nordspets artfynd.xlsx
+++ b/artfynd/Ornös nordspets artfynd.xlsx
@@ -22908,7 +22908,7 @@
         <v>136730156</v>
       </c>
       <c r="B191" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>

--- a/artfynd/Ornös nordspets artfynd.xlsx
+++ b/artfynd/Ornös nordspets artfynd.xlsx
@@ -22908,7 +22908,7 @@
         <v>136730156</v>
       </c>
       <c r="B191" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>

--- a/artfynd/Ornös nordspets artfynd.xlsx
+++ b/artfynd/Ornös nordspets artfynd.xlsx
@@ -22908,7 +22908,7 @@
         <v>136730156</v>
       </c>
       <c r="B191" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
